--- a/artfynd/A 23854-2025 artfynd.xlsx
+++ b/artfynd/A 23854-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,6 +785,103 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126022889</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79054</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>556373</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6972407</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23854-2025 artfynd.xlsx
+++ b/artfynd/A 23854-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>126022889</v>
       </c>
       <c r="B3" t="n">
-        <v>79054</v>
+        <v>79058</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23854-2025 artfynd.xlsx
+++ b/artfynd/A 23854-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>126022889</v>
       </c>
       <c r="B3" t="n">
-        <v>79058</v>
+        <v>79059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23854-2025 artfynd.xlsx
+++ b/artfynd/A 23854-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>126022889</v>
       </c>
       <c r="B3" t="n">
-        <v>79059</v>
+        <v>79063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23854-2025 artfynd.xlsx
+++ b/artfynd/A 23854-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,6 +883,119 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126421052</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56848</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brantbergtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>556361</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6972534</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23854-2025 artfynd.xlsx
+++ b/artfynd/A 23854-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>126022889</v>
       </c>
       <c r="B3" t="n">
-        <v>79063</v>
+        <v>79066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126421052</v>
       </c>
       <c r="B4" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23854-2025 artfynd.xlsx
+++ b/artfynd/A 23854-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>104451214</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556300.1880069081</v>
+        <v>556300</v>
       </c>
       <c r="R2" t="n">
-        <v>6972580.209520392</v>
+        <v>6972580</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -791,11 +786,11 @@
         <v>126022889</v>
       </c>
       <c r="B3" t="n">
-        <v>79066</v>
+        <v>79413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -888,7 +883,7 @@
         <v>126421052</v>
       </c>
       <c r="B4" t="n">
-        <v>56849</v>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,6 +990,204 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>81142548</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>556285</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6972453</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-10-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-10-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126022920</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>556397</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6972476</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23854-2025 artfynd.xlsx
+++ b/artfynd/A 23854-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104451214</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022889</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126421052</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81142548</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,8 +1213,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022920</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>